--- a/rmonize/data_dictionary/DD_BGS98_P2.xlsx
+++ b/rmonize/data_dictionary/DD_BGS98_P2.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:D60"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -843,12 +843,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MIausl</t>
+          <t>MIlandB</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ausländ. Staatsangehörigkeit (lt. Einwohnermeldeamt)</t>
+          <t>Geburtsland Deutschland</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -863,17 +863,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>LBcholx</t>
+          <t>MIstaat_m1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Cholesterin gesamt [mg/dl]</t>
+          <t>Staatsangehörigkeit: Deutsch</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>integer</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>LBldlB</t>
+          <t>LBcholx</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>LDL-Cholesterin, berechnet nach Friedewald-Formel [mmol/l]</t>
+          <t>Cholesterin gesamt [mg/dl]</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -903,12 +903,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>LBhdl</t>
+          <t>LBldlB</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>HDL-Cholesterin [mmol/l]</t>
+          <t>LDL-Cholesterin, berechnet nach Friedewald-Formel [mmol/l]</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -923,12 +923,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>USbmi</t>
+          <t>LBhdl</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Body-Mass-Index [kg/m²]</t>
+          <t>HDL-Cholesterin [mmol/l]</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -943,12 +943,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>USbmi_FUP</t>
+          <t>USbmi</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Body Mass Index at follow-up [kg/m²]</t>
+          <t>Body-Mass-Index [kg/m²]</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -963,12 +963,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>UStail</t>
+          <t>USbmi_FUP</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Taillenumfang [cm]</t>
+          <t>Body Mass Index at follow-up [kg/m²]</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -983,12 +983,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>UStail_FUP</t>
+          <t>UStail</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Taillenumfang at follow-up [cm]</t>
+          <t>Taillenumfang [cm]</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>UShuef</t>
+          <t>UStail_FUP</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Hüftumfang [cm]</t>
+          <t>Taillenumfang at follow-up [cm]</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1023,12 +1023,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>UShuef_FUP</t>
+          <t>UShuef</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Hüftumfang at follow-up [cm]</t>
+          <t>Hüftumfang [cm]</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Gcal</t>
+          <t>UShuef_FUP</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Kcal/d</t>
+          <t>Hüftumfang at follow-up [cm]</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1063,12 +1063,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>GZK</t>
+          <t>Gcal</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>KH [g/d]</t>
+          <t>Kcal/d</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1083,12 +1083,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>GZE</t>
+          <t>GZK</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Protein [g/d]</t>
+          <t>KH [g/d]</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>GZF</t>
+          <t>GZE</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Fett [g/d]</t>
+          <t>Protein [g/d]</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>GZA</t>
+          <t>GZF</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Alkohol [g/d]</t>
+          <t>Fett [g/d]</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>GZB</t>
+          <t>GZA</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ballasts [g/d]</t>
+          <t>Alkohol [g/d]</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1163,12 +1163,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>GFP</t>
+          <t>GZB</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>polyunges FS [g/d]</t>
+          <t>Ballasts [g/d]</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1183,12 +1183,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>GMNa</t>
+          <t>GFP</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Natrium[g/d]</t>
+          <t>polyunges FS [g/d]</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>GpMK</t>
+          <t>GMNa</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Kalium [g/d]</t>
+          <t>Natrium[g/d]</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>KUCHKEKS</t>
+          <t>GpMK</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Kuchen,Kekse[g/d]</t>
+          <t>Kalium [g/d]</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1243,12 +1243,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SAFT</t>
+          <t>GFS</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Obst,Gemüsesäfte [g/d]</t>
+          <t>ges.FS (g/d)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1263,12 +1263,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SOFTDRNK</t>
+          <t>GFU</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Erfrischungsgetränke [g/d]</t>
+          <t>unges.FS (g/d)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1283,12 +1283,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>FLEISCHW</t>
+          <t>GKD</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Fleisch, Wild [g/d]</t>
+          <t>Disacch (g/d)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1303,12 +1303,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>KAFFEE</t>
+          <t>GKM</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Kaffee [g/d]</t>
+          <t>Monosacch (g/d)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>TEE</t>
+          <t>AGE_ANTH_FUP</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Tee [g/d]</t>
+          <t>Age at anthropometric measurement at follow-up [years]</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>GEMPILZE</t>
+          <t>KUCHKEKS</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Gemüse,Pilze [g/d]</t>
+          <t>Kuchen,Kekse[g/d]</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>BLATTKRT</t>
+          <t>SAFT</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Blattgemüse,Kräuter [g/d]</t>
+          <t>Obst,Gemüsesäfte [g/d]</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1383,12 +1383,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>KOHLGEM</t>
+          <t>SOFTDRNK</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Kohlgemüse [g/d]</t>
+          <t>Erfrischungsgetränke [g/d]</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SUESSES</t>
+          <t>FLEISCHW</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Süsses [g/d]</t>
+          <t>Fleisch, Wild [g/d]</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1423,15 +1423,135 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
+          <t>KAFFEE</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Kaffee [g/d]</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>decimal</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>TEE</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Tee [g/d]</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>decimal</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>GEMPILZE</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Gemüse,Pilze [g/d]</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>decimal</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>BLATTKRT</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Blattgemüse,Kräuter [g/d]</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>decimal</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>KOHLGEM</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Kohlgemüse [g/d]</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>decimal</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>SUESSES</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Süsses [g/d]</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>decimal</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
           <t>WURST</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>Wurst [g/d]</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>decimal</t>
         </is>
@@ -1444,7 +1564,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -2120,7 +2240,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>MIausl</t>
+          <t>MIlandB</t>
         </is>
       </c>
       <c r="B38">
@@ -2128,7 +2248,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Ausländer</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="D38" t="b">
@@ -2138,37 +2258,19 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>MIausl</t>
+          <t>MIstaat_m1</t>
         </is>
       </c>
       <c r="B39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Kein Ausländer</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="D39" t="b">
         <v>0</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>MIausl</t>
-        </is>
-      </c>
-      <c r="B40">
-        <v>-97</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Nicht erhoben</t>
-        </is>
-      </c>
-      <c r="D40" t="b">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
